--- a/owlcms/src/main/resources/templates/jury/JuryExam-A4.xlsx
+++ b/owlcms/src/main/resources/templates/jury/JuryExam-A4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\jury\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\jury\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC6C164-A8A4-45D4-BBD4-ED2B2A055E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A947A721-B0C9-4F01-867A-793BD3C9F5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40245" yWindow="-4080" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jury" sheetId="1" r:id="rId1"/>
@@ -75,9 +75,6 @@
     <t>${competition.competitionSite}</t>
   </si>
   <si>
-    <t>${competition.competitionDate}</t>
-  </si>
-  <si>
     <t>${session.referee1}</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>${t.get("Jury.incorrect.Title")}</t>
+  </si>
+  <si>
+    <t>${session.competitionTimeAsExcelDate}</t>
   </si>
 </sst>
 </file>
@@ -761,26 +761,26 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -798,15 +798,7 @@
     <cellStyle name="Titre 1 1 1 1 1" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="Titre de la feuille" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1349,7 +1341,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -1365,7 +1357,7 @@
     </row>
     <row r="2" spans="1:12" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="54"/>
       <c r="C2" s="2" t="s">
@@ -1377,16 +1369,16 @@
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
       <c r="I2" s="28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="54"/>
       <c r="C3" s="55" t="s">
@@ -1396,23 +1388,23 @@
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
       <c r="G3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="36" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="49" t="s">
         <v>1</v>
@@ -1423,10 +1415,10 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="26"/>
     </row>
@@ -1437,12 +1429,12 @@
       <c r="C6" s="7"/>
       <c r="D6" s="8"/>
       <c r="F6" s="50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="51"/>
       <c r="H6" s="52"/>
       <c r="I6" s="51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" s="51"/>
       <c r="K6" s="53"/>
@@ -1452,14 +1444,14 @@
         <v>0</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="F7" s="9">
         <v>1</v>
@@ -1482,22 +1474,22 @@
     </row>
     <row r="8" spans="1:12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="39" t="s">
         <v>24</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>25</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -1508,7 +1500,7 @@
     </row>
     <row r="10" spans="1:12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1524,18 +1516,18 @@
     </row>
     <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
       <c r="E12" s="18"/>
       <c r="F12" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="19"/>
       <c r="H12" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I12" s="43"/>
       <c r="J12" s="44"/>
@@ -1769,21 +1761,16 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11 C12 J12">
-    <cfRule type="expression" dxfId="3" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="8" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D10">
-    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E10">
+  <conditionalFormatting sqref="D9:E10">
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
@@ -1823,7 +1810,7 @@
   <sheetData>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="54"/>
       <c r="C2" s="2" t="s">
@@ -1835,16 +1822,16 @@
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
       <c r="I2" s="28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="54"/>
       <c r="C3" s="55" t="s">
@@ -1854,23 +1841,23 @@
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
       <c r="G3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="36" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="49" t="s">
         <v>1</v>
@@ -1879,10 +1866,10 @@
       <c r="E4" s="49"/>
       <c r="F4" s="22"/>
       <c r="I4" s="28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="26"/>
     </row>
@@ -1907,40 +1894,40 @@
     <row r="7" spans="1:11" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
       <c r="F7" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="I7" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="J7" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="K7" s="29" t="s">
         <v>35</v>
-      </c>
-      <c r="K7" s="29" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="65"/>
+        <v>11</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="61"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
@@ -1951,13 +1938,13 @@
     <row r="9" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="65"/>
+        <v>12</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
       <c r="H9" s="31"/>
@@ -1968,13 +1955,13 @@
     <row r="10" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="65"/>
+        <v>13</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="62"/>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
@@ -1995,18 +1982,18 @@
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
       <c r="E12" s="18"/>
       <c r="F12" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="19"/>
       <c r="H12" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I12" s="43"/>
       <c r="J12" s="44"/>
@@ -2025,182 +2012,182 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20"/>
-      <c r="B14" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
+      <c r="B14" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20"/>
-      <c r="B15" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
+      <c r="B15" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20"/>
-      <c r="B16" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
+      <c r="B16" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20"/>
-      <c r="B17" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
+      <c r="B17" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20"/>
-      <c r="B18" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
+      <c r="B18" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="20"/>
-      <c r="B19" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
+      <c r="B19" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="20"/>
-      <c r="B20" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
+      <c r="B20" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20"/>
-      <c r="B21" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
+      <c r="B21" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="20"/>
-      <c r="B22" s="60" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
+      <c r="B22" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
     </row>
     <row r="23" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="20"/>
-      <c r="B23" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
+      <c r="B23" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
     </row>
     <row r="24" spans="1:11" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="20"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
     </row>
     <row r="25" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
@@ -2213,19 +2200,17 @@
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
       <c r="K25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="B24:F24"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="G14:K14"/>
     <mergeCell ref="B22:F22"/>
@@ -2242,12 +2227,14 @@
     <mergeCell ref="G16:K16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="G17:K17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:C11 J12 C12:C13 B13 C25">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
